--- a/data/trans_dic/P04D$colectiva-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/P04D$colectiva-Habitat-trans_dic.xlsx
@@ -524,7 +524,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que, al menos, tiene calefacción colectiva en su vivienda</t>
+          <t>Población que, al menos, tiene calefacción colectiva en su vivienda (tasa de respuesta: 99,87%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -678,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1,59; 4,3</t>
+          <t>1,5; 4,06</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,58; 2,34</t>
+          <t>0,59; 2,44</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>3,97; 7,33</t>
+          <t>3,91; 7,19</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>1,17; 3,56</t>
+          <t>1,14; 3,59</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>1,33; 3,61</t>
+          <t>1,33; 3,69</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>4,12; 7,14</t>
+          <t>4,02; 7,13</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>1,63; 3,33</t>
+          <t>1,64; 3,26</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>1,12; 2,6</t>
+          <t>1,14; 2,49</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>4,41; 6,61</t>
+          <t>4,46; 6,67</t>
         </is>
       </c>
     </row>
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>2,45; 4,82</t>
+          <t>2,43; 4,88</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,81; 2,41</t>
+          <t>0,78; 2,28</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2,4; 6,73</t>
+          <t>2,32; 6,79</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>2,43; 4,73</t>
+          <t>2,43; 4,87</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,46; 1,64</t>
+          <t>0,45; 1,65</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>5,53; 8,46</t>
+          <t>5,49; 8,39</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,7; 4,43</t>
+          <t>2,73; 4,47</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,75; 1,72</t>
+          <t>0,76; 1,75</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>3,87; 6,97</t>
+          <t>3,96; 7,07</t>
         </is>
       </c>
     </row>
@@ -898,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,27; 1,67</t>
+          <t>0,27; 1,63</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,98; 3,24</t>
+          <t>1,01; 3,33</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>3,14; 7,04</t>
+          <t>3,12; 6,95</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,26; 1,45</t>
+          <t>0,26; 1,47</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>1,19; 3,31</t>
+          <t>1,22; 3,42</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1,1; 3,66</t>
+          <t>1,2; 3,68</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,39; 1,24</t>
+          <t>0,39; 1,3</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>1,32; 2,81</t>
+          <t>1,3; 2,81</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>2,13; 4,51</t>
+          <t>2,07; 4,45</t>
         </is>
       </c>
     </row>
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>3,76; 6,5</t>
+          <t>3,84; 6,56</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>4,67; 7,9</t>
+          <t>4,67; 7,84</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>6,75; 11,09</t>
+          <t>6,86; 11,33</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>2,77; 5,18</t>
+          <t>2,77; 5,14</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>3,31; 6,14</t>
+          <t>3,34; 6,07</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>6,02; 9,35</t>
+          <t>6,19; 9,45</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>3,47; 5,4</t>
+          <t>3,56; 5,4</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>4,22; 6,46</t>
+          <t>4,35; 6,46</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>6,92; 9,66</t>
+          <t>6,98; 9,66</t>
         </is>
       </c>
     </row>
@@ -1118,47 +1118,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>2,55; 3,78</t>
+          <t>2,57; 3,82</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>2,27; 3,41</t>
+          <t>2,26; 3,42</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>4,55; 6,9</t>
+          <t>4,52; 6,95</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>2,14; 3,33</t>
+          <t>2,16; 3,32</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>2,0; 3,02</t>
+          <t>1,98; 3,03</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,77; 6,68</t>
+          <t>4,74; 6,54</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,5; 3,33</t>
+          <t>2,54; 3,36</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>2,27; 3,04</t>
+          <t>2,26; 3,05</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>5,02; 6,51</t>
+          <t>4,99; 6,51</t>
         </is>
       </c>
     </row>
@@ -1210,7 +1210,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que, al menos, tiene calefacción colectiva en su vivienda</t>
+          <t>Población que, al menos, tiene calefacción colectiva en su vivienda (tasa de respuesta: 99,87%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1417,47 +1417,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>11173; 30107</t>
+          <t>10489; 28462</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>3909; 15777</t>
+          <t>3967; 16485</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>25168; 46439</t>
+          <t>24762; 45520</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>8137; 24777</t>
+          <t>7934; 25018</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>8939; 24300</t>
+          <t>8963; 24823</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>29859; 51746</t>
+          <t>29166; 51638</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>22790; 46543</t>
+          <t>22841; 45473</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>15145; 35045</t>
+          <t>15356; 33528</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>59881; 89802</t>
+          <t>60595; 90618</t>
         </is>
       </c>
     </row>
@@ -1580,47 +1580,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>24866; 48918</t>
+          <t>24635; 49548</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>8314; 24658</t>
+          <t>8022; 23346</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>28650; 80263</t>
+          <t>27636; 80884</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>25049; 48712</t>
+          <t>25078; 50124</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>4818; 17102</t>
+          <t>4714; 17207</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>52876; 80952</t>
+          <t>52465; 80232</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>55255; 90570</t>
+          <t>55736; 91303</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>15490; 35466</t>
+          <t>15774; 36047</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>83233; 149692</t>
+          <t>85163; 151825</t>
         </is>
       </c>
     </row>
@@ -1743,47 +1743,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>2042; 12647</t>
+          <t>2056; 12321</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>7420; 24636</t>
+          <t>7635; 25263</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>22126; 49512</t>
+          <t>21969; 48916</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>1980; 11258</t>
+          <t>1985; 11442</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>9365; 25985</t>
+          <t>9607; 26860</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>10249; 34079</t>
+          <t>11130; 34320</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>5906; 19021</t>
+          <t>5955; 19945</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>20376; 43454</t>
+          <t>20049; 43403</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>34908; 73714</t>
+          <t>33768; 72786</t>
         </is>
       </c>
     </row>
@@ -1906,47 +1906,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>35608; 61569</t>
+          <t>36435; 62199</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>43801; 74059</t>
+          <t>43769; 73501</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>62446; 102534</t>
+          <t>63395; 104744</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>29165; 54498</t>
+          <t>29183; 54021</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>34544; 64108</t>
+          <t>34904; 63354</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>65783; 102074</t>
+          <t>67632; 103193</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>69340; 108033</t>
+          <t>71112; 107897</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>83613; 127952</t>
+          <t>86270; 127974</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>139494; 194894</t>
+          <t>140855; 194829</t>
         </is>
       </c>
     </row>
@@ -2069,47 +2069,47 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>87160; 129163</t>
+          <t>87767; 130727</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>76959; 115788</t>
+          <t>76700; 116207</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>157265; 238211</t>
+          <t>156025; 240011</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>76214; 118292</t>
+          <t>76675; 117981</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>70912; 107083</t>
+          <t>70305; 107476</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>176683; 247518</t>
+          <t>175549; 242422</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>174013; 232053</t>
+          <t>177222; 234637</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>157173; 211025</t>
+          <t>156731; 211574</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>359613; 465817</t>
+          <t>357292; 466268</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P04D$colectiva-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/P04D$colectiva-Habitat-trans_dic.xlsx
@@ -635,7 +635,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>5,36%</t>
+          <t>4,92%</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -650,7 +650,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>5,58%</t>
+          <t>5,68%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -665,7 +665,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>5,48%</t>
+          <t>5,31%</t>
         </is>
       </c>
     </row>
@@ -678,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1,5; 4,06</t>
+          <t>1,54; 4,21</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,59; 2,44</t>
+          <t>0,58; 2,44</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>3,91; 7,19</t>
+          <t>3,56; 6,59</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>1,14; 3,59</t>
+          <t>1,18; 3,64</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>1,33; 3,69</t>
+          <t>1,33; 3,49</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>4,02; 7,13</t>
+          <t>4,49; 7,35</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>1,64; 3,26</t>
+          <t>1,64; 3,4</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>1,14; 2,49</t>
+          <t>1,19; 2,5</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>4,46; 6,67</t>
+          <t>4,36; 6,45</t>
         </is>
       </c>
     </row>
@@ -745,7 +745,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>4,78%</t>
+          <t>5,21%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>6,87%</t>
+          <t>6,34%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -775,7 +775,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>5,71%</t>
+          <t>5,78%</t>
         </is>
       </c>
     </row>
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>2,43; 4,88</t>
+          <t>2,51; 5,1</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,78; 2,28</t>
+          <t>0,86; 2,42</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2,32; 6,79</t>
+          <t>3,98; 6,73</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>2,43; 4,87</t>
+          <t>2,33; 4,74</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,45; 1,65</t>
+          <t>0,47; 1,67</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>5,49; 8,39</t>
+          <t>5,2; 7,78</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,73; 4,47</t>
+          <t>2,72; 4,44</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,76; 1,75</t>
+          <t>0,76; 1,76</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>3,96; 7,07</t>
+          <t>4,88; 6,81</t>
         </is>
       </c>
     </row>
@@ -855,7 +855,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>4,6%</t>
+          <t>5,04%</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -870,7 +870,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>2,47%</t>
+          <t>3,49%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -885,7 +885,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>3,39%</t>
+          <t>4,26%</t>
         </is>
       </c>
     </row>
@@ -903,42 +903,42 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1,01; 3,33</t>
+          <t>1,07; 3,24</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>3,12; 6,95</t>
+          <t>3,42; 6,96</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,26; 1,47</t>
+          <t>0,25; 1,4</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>1,22; 3,42</t>
+          <t>1,19; 3,4</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1,2; 3,68</t>
+          <t>2,43; 4,89</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,39; 1,3</t>
+          <t>0,39; 1,23</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>1,3; 2,81</t>
+          <t>1,3; 2,79</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>2,07; 4,45</t>
+          <t>3,25; 5,44</t>
         </is>
       </c>
     </row>
@@ -965,7 +965,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>8,68%</t>
+          <t>7,94%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -980,7 +980,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>7,86%</t>
+          <t>8,12%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -995,7 +995,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>8,23%</t>
+          <t>8,03%</t>
         </is>
       </c>
     </row>
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>3,84; 6,56</t>
+          <t>3,73; 6,49</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>4,67; 7,84</t>
+          <t>4,76; 7,7</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>6,86; 11,33</t>
+          <t>6,41; 10,12</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>2,77; 5,14</t>
+          <t>2,77; 5,13</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>3,34; 6,07</t>
+          <t>3,29; 6,17</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>6,19; 9,45</t>
+          <t>6,78; 9,54</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>3,56; 5,4</t>
+          <t>3,55; 5,26</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>4,35; 6,46</t>
+          <t>4,32; 6,32</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>6,98; 9,66</t>
+          <t>7,01; 9,15</t>
         </is>
       </c>
     </row>
@@ -1075,7 +1075,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>5,89%</t>
+          <t>5,88%</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1090,7 +1090,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>5,8%</t>
+          <t>6,12%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1105,7 +1105,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>5,85%</t>
+          <t>6,01%</t>
         </is>
       </c>
     </row>
@@ -1118,47 +1118,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>2,57; 3,82</t>
+          <t>2,52; 3,79</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>2,26; 3,42</t>
+          <t>2,3; 3,42</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>4,52; 6,95</t>
+          <t>5,14; 6,72</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>2,16; 3,32</t>
+          <t>2,13; 3,29</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>1,98; 3,03</t>
+          <t>2,01; 3,06</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,74; 6,54</t>
+          <t>5,44; 6,84</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,54; 3,36</t>
+          <t>2,54; 3,41</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>2,26; 3,05</t>
+          <t>2,27; 3,07</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>4,99; 6,51</t>
+          <t>5,46; 6,56</t>
         </is>
       </c>
     </row>
@@ -1374,7 +1374,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>33933</t>
+          <t>33881</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -1389,7 +1389,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>40469</t>
+          <t>41698</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>74401</t>
+          <t>75579</t>
         </is>
       </c>
     </row>
@@ -1417,47 +1417,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>10489; 28462</t>
+          <t>10811; 29514</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>3967; 16485</t>
+          <t>3885; 16457</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>24762; 45520</t>
+          <t>24531; 45403</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>7934; 25018</t>
+          <t>8216; 25330</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>8963; 24823</t>
+          <t>8979; 23471</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>29166; 51638</t>
+          <t>32932; 53936</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>22841; 45473</t>
+          <t>22886; 47529</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>15356; 33528</t>
+          <t>15996; 33697</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>60595; 90618</t>
+          <t>62006; 91690</t>
         </is>
       </c>
     </row>
@@ -1537,7 +1537,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>56992</t>
+          <t>54593</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -1552,7 +1552,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>65697</t>
+          <t>67717</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1567,7 +1567,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>122689</t>
+          <t>122310</t>
         </is>
       </c>
     </row>
@@ -1580,47 +1580,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>24635; 49548</t>
+          <t>25424; 51748</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>8022; 23346</t>
+          <t>8775; 24749</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>27636; 80884</t>
+          <t>41703; 70482</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>25078; 50124</t>
+          <t>23954; 48858</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>4714; 17207</t>
+          <t>4851; 17442</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>52465; 80232</t>
+          <t>55540; 83041</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>55736; 91303</t>
+          <t>55548; 90757</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>15774; 36047</t>
+          <t>15603; 36260</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>85163; 151825</t>
+          <t>103338; 144106</t>
         </is>
       </c>
     </row>
@@ -1700,7 +1700,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>32372</t>
+          <t>40209</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1715,7 +1715,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>22998</t>
+          <t>28282</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1730,7 +1730,7 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>55370</t>
+          <t>68491</t>
         </is>
       </c>
     </row>
@@ -1743,47 +1743,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>2056; 12321</t>
+          <t>2044; 12302</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>7635; 25263</t>
+          <t>8148; 24630</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>21969; 48916</t>
+          <t>27289; 55545</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>1985; 11442</t>
+          <t>1976; 10892</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>9607; 26860</t>
+          <t>9365; 26675</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>11130; 34320</t>
+          <t>19682; 39577</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>5955; 19945</t>
+          <t>5917; 18866</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>20049; 43403</t>
+          <t>20011; 43056</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>33768; 72786</t>
+          <t>52255; 87540</t>
         </is>
       </c>
     </row>
@@ -1863,7 +1863,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>80245</t>
+          <t>78397</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1878,7 +1878,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>85782</t>
+          <t>90592</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1893,7 +1893,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>166027</t>
+          <t>168989</t>
         </is>
       </c>
     </row>
@@ -1906,47 +1906,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>36435; 62199</t>
+          <t>35387; 61496</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>43769; 73501</t>
+          <t>44595; 72201</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>63395; 104744</t>
+          <t>63346; 99931</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>29183; 54021</t>
+          <t>29126; 53959</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>34904; 63354</t>
+          <t>34303; 64449</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>67632; 103193</t>
+          <t>75679; 106495</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>71112; 107897</t>
+          <t>70888; 105220</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>86270; 127974</t>
+          <t>85509; 125246</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>140855; 194829</t>
+          <t>147545; 192430</t>
         </is>
       </c>
     </row>
@@ -2026,7 +2026,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>203541</t>
+          <t>207080</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -2041,7 +2041,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>214947</t>
+          <t>228289</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -2056,7 +2056,7 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>418488</t>
+          <t>435368</t>
         </is>
       </c>
     </row>
@@ -2069,47 +2069,47 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>87767; 130727</t>
+          <t>86186; 129469</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>76700; 116207</t>
+          <t>77926; 115937</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>156025; 240011</t>
+          <t>181171; 236711</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>76675; 117981</t>
+          <t>75749; 116826</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>70305; 107476</t>
+          <t>71198; 108427</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>175549; 242422</t>
+          <t>202710; 254958</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>177222; 234637</t>
+          <t>177480; 238128</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>156731; 211574</t>
+          <t>157320; 213105</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>357292; 466268</t>
+          <t>396060; 475223</t>
         </is>
       </c>
     </row>
